--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e958aba48d0575</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=422b5002f3c92e96</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca947b911b13d47</t>
+          <t>https://www.indeed.com/viewjob?jk=59c6b7befce247af</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2762492ad7551efe</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59c6b7befce247af</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a924e0d6d13cba9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frame Foxes Creative</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Frame Foxes Creative</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=898613f236f4ba90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=9dad0013a3f08c65</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=03347f4108a525d3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=964ce39a36051ef8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a68f594cdedbebc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5e9db015bd73d0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,137 +1546,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=7954eae53dc1a960</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e319e5ec133537</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9729cda6029482</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=158355a9a64dd1b3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6f2e725c3841f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1821921db4210a68</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ff455df1f6f6c2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4aad71a748b31b69</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=45ace5d539e9097b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=8df5f5c1ab715a31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=135584a59f00c4db</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=4be624c16359ee5a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f244c871d2cf53</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9e130e5057c468</t>
+          <t>https://www.indeed.com/viewjob?jk=cbce7069c299cc5b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f42b8dd196f861</t>
+          <t>https://www.indeed.com/viewjob?jk=64b6ccd45972633d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff8e0f386ef907b</t>
+          <t>https://www.indeed.com/viewjob?jk=f532a047e4cbdddd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=150ec26629269c1f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b89f3d7d4d597f4b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=d6abc20edf0fd8f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=20edf635d258b075</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e191e53db17b1c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Senior</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mister Car Wash</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c744355a461cd5a5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III (CJIS)</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>County of San Luis Obispo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+          <t>https://www.indeed.com/viewjob?jk=49d2cd77f2f714ce</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4f16b165a8197</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=b5808a3926a706c6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=a3ef83e1dea6414e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>isolved</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nixa, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+          <t>https://www.indeed.com/viewjob?jk=2f82629fcb7c3273</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2861181bdf3a3141</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=51241aaf49f62a1e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8ad2dd9097d275</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=3c86f25472be8f86</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5a072087da2b1c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=32be597d03461cf2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c3efcbf365ec3b20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0891382aedc90402</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=46a465b7547449b2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, IAM, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2f5cef76808163a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e68b70053b2a99e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=afad00ed0230efba</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+          <t>https://www.indeed.com/viewjob?jk=90c464e383e34580</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,40 +3086,5115 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4886c7943d95fde</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf2cd6ff1af9152f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddd026ed04aff3f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1443de690608f973</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fafe5f457265140c</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee0c9efe263252c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=134da4ed5371e690</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cec5522637756cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bce59916a631c229</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d9800315a487a07</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=944c909e8090f77c</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9f08c0f9ab8ce8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63bc0adc99f8a24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f643c2f9e2f8e875</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ff781ad106bf00e</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0e7e3a50b44eadc</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d95cfc0fb1f0052b</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=237407f225bdbdde</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee5fb899d70bb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a61b9f987d8319</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77dcd59570e17714</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=281137e24698eadf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ef1c49ca890a02d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a7925bf814317b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db200a070bd6f170</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85e48f3b0c65cee2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d84570080ccefe4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=415547713e005c9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dec000a9308e1a29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e1ea9f10fd1fc07</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a80a106f8cc412</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a49b62e5c57fb30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e98585cc9b7a9700</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15db2953c1e3b688</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d7c175920fe1515</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a84e5fecd3d8a56</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f51834cb7830783</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06941a936b5627f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbd6eb878651cec7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=319f7679b0c236b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98788b7051be7608</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=269f6b09b3801d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7be632d37eec0b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fd7ad62dd171a18</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85df90bb6dfbfae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e11ec725a2ebb03</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eada5f5f6db8d5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=258bed23fe0cbda2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e819a7e5906d69f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b862bc47d421e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db5fbc30263e47f</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e3a8e2d05c0771</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Cloud Platforms Engineer II</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Amcor</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Oshkosh, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Books-A-Million</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1821921db4210a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d82519a3cff7a03c</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48aa35823006036d</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2409f88dc2bb6479</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05589bd86f6613ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f5bbf7634b17efe</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=842b00d75a1fdb78</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6426664fe876ccf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46c1e283728ccf2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da466b24aa8b8f93</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=171623610154829e</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bad93f8dd31cb04f</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6531397ce3761368</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b74c85c575d7d6ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c4599945fd6770f</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c2f5e00614cd1e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f61287d3dfc60c6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71c3abbc6d6ae00c</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca0a972a4b0fc1ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a9fe046872a5db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63dc4567cdb8f559</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81a5e57062f4e1d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d0b7df132fd9dd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d5681ee5fb7bccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efde12506dd5e02e</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1d92d7fbbbc81d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ed8322b5b26962</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f7de5560f7c15c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fef70d9dc7c7945e</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a1dddfb2596b7d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e02a9496819a565</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d55e53d1a36497d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0e29080468d4f19</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=000b04871f739cd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41ab2f0cbeb867c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d314e0fbc6c7255a</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff5a5de7290a2c8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5794a14a29c1f8c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b7c1c8f63656a2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7482709c6153e607</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9d47ad9f886f7d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f52ec397c45d4e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a30e01f59bf80aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ec7b21cec928d78</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48557644ca27af91</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38816cfaaf11a6ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Cloud Database Administrator- Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23bfa150bf370564</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Assistant Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Software Engineer II - AI Solutions</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>U.S. Marine Corps</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Quantico, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Investment Compliance Engineer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Apollo</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Highlights for Children</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>isolved</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Nixa, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PIMS Data Analyst</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Bechtel</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Senior</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Mister Car Wash</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Software Engineer III (CJIS)</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>County of San Luis Obispo</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Batch Operations</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>RDS, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e05d25284fdf864</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Software Developer - Information Governance</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PowerBI Developer</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Senior Cloud &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Prologis</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Anteriad</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Apptronik</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Data/ Application Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Charlie's Produce</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CERTIFID</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
           <t>BI Developer Mid or Senior</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Progressive</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D222" t="n">
         <v>10.4</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Engineer (AIA)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59c6b7befce247af</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=59c6b7befce247af</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frame Foxes Creative</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Frame Foxes Creative</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898613f236f4ba90</t>
+          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dad0013a3f08c65</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03347f4108a525d3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964ce39a36051ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a68f594cdedbebc</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5e9db015bd73d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7954eae53dc1a960</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9729cda6029482</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158355a9a64dd1b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,15 +1633,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6f2e725c3841f</t>
+          <t>https://www.indeed.com/viewjob?jk=90c464e383e34580</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,15 +1668,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ff455df1f6f6c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4886c7943d95fde</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,15 +1703,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aad71a748b31b69</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2cd6ff1af9152f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,15 +1738,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ace5d539e9097b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd026ed04aff3f7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,15 +1773,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df5f5c1ab715a31</t>
+          <t>https://www.indeed.com/viewjob?jk=1443de690608f973</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,15 +1808,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=135584a59f00c4db</t>
+          <t>https://www.indeed.com/viewjob?jk=fafe5f457265140c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,15 +1843,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4be624c16359ee5a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0c9efe263252c2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,15 +1878,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f244c871d2cf53</t>
+          <t>https://www.indeed.com/viewjob?jk=134da4ed5371e690</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbce7069c299cc5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec5522637756cf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b6ccd45972633d</t>
+          <t>https://www.indeed.com/viewjob?jk=bce59916a631c229</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,15 +1983,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f532a047e4cbdddd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9800315a487a07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,15 +2018,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=150ec26629269c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=944c909e8090f77c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,15 +2053,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b89f3d7d4d597f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f08c0f9ab8ce8d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6abc20edf0fd8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=63bc0adc99f8a24b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,15 +2123,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20edf635d258b075</t>
+          <t>https://www.indeed.com/viewjob?jk=f643c2f9e2f8e875</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,15 +2158,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e191e53db17b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff781ad106bf00e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c744355a461cd5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e7e3a50b44eadc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,15 +2228,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d2cd77f2f714ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d95cfc0fb1f0052b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,15 +2263,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4f16b165a8197</t>
+          <t>https://www.indeed.com/viewjob?jk=237407f225bdbdde</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,15 +2298,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5808a3926a706c6</t>
+          <t>https://www.indeed.com/viewjob?jk=eee5fb899d70bb38</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,15 +2333,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3ef83e1dea6414e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a61b9f987d8319</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,15 +2368,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f82629fcb7c3273</t>
+          <t>https://www.indeed.com/viewjob?jk=77dcd59570e17714</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,15 +2403,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2861181bdf3a3141</t>
+          <t>https://www.indeed.com/viewjob?jk=281137e24698eadf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51241aaf49f62a1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef1c49ca890a02d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8ad2dd9097d275</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a7925bf814317b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,15 +2508,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c86f25472be8f86</t>
+          <t>https://www.indeed.com/viewjob?jk=db200a070bd6f170</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,15 +2543,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5a072087da2b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48f3b0c65cee2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,15 +2578,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32be597d03461cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=d84570080ccefe4b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,15 +2613,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3efcbf365ec3b20</t>
+          <t>https://www.indeed.com/viewjob?jk=415547713e005c9b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,15 +2648,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0891382aedc90402</t>
+          <t>https://www.indeed.com/viewjob?jk=dec000a9308e1a29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,15 +2683,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a465b7547449b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1ea9f10fd1fc07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e68b70053b2a99e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a80a106f8cc412</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps-CI/CD Pipeline Specialist - Project Delivery Senior Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, MongoDB, Cassandra, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afad00ed0230efba</t>
+          <t>https://www.indeed.com/viewjob?jk=3a49b62e5c57fb30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=e98585cc9b7a9700</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=15db2953c1e3b688</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7c175920fe1515</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a84e5fecd3d8a56</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f51834cb7830783</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=06941a936b5627f3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=dbd6eb878651cec7</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c464e383e34580</t>
+          <t>https://www.indeed.com/viewjob?jk=319f7679b0c236b3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4886c7943d95fde</t>
+          <t>https://www.indeed.com/viewjob?jk=98788b7051be7608</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2cd6ff1af9152f</t>
+          <t>https://www.indeed.com/viewjob?jk=269f6b09b3801d42</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd026ed04aff3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7be632d37eec0b45</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1443de690608f973</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd7ad62dd171a18</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafe5f457265140c</t>
+          <t>https://www.indeed.com/viewjob?jk=85df90bb6dfbfae8</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0c9efe263252c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9e11ec725a2ebb03</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134da4ed5371e690</t>
+          <t>https://www.indeed.com/viewjob?jk=7eada5f5f6db8d5e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec5522637756cf</t>
+          <t>https://www.indeed.com/viewjob?jk=258bed23fe0cbda2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce59916a631c229</t>
+          <t>https://www.indeed.com/viewjob?jk=e819a7e5906d69f9</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9800315a487a07</t>
+          <t>https://www.indeed.com/viewjob?jk=2b862bc47d421e21</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944c909e8090f77c</t>
+          <t>https://www.indeed.com/viewjob?jk=0db5fbc30263e47f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f08c0f9ab8ce8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63bc0adc99f8a24b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f643c2f9e2f8e875</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Cloud Platforms Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Oshkosh, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,137 +3576,137 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff781ad106bf00e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e7e3a50b44eadc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95cfc0fb1f0052b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>AWS Cloud Architect - Remote - Contract</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navat Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=237407f225bdbdde</t>
+          <t>https://www.indeed.com/viewjob?jk=21d6094d4c650121</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee5fb899d70bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=1821921db4210a68</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Assistant Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a61b9f987d8319</t>
+          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77dcd59570e17714</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281137e24698eadf</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef1c49ca890a02d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a7925bf814317b</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db200a070bd6f170</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,67 +3961,67 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48f3b0c65cee2</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84570080ccefe4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415547713e005c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec000a9308e1a29</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1ea9f10fd1fc07</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a80a106f8cc412</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4157,11 +4157,11 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a49b62e5c57fb30</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98585cc9b7a9700</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>isolved</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nixa, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db2953c1e3b688</t>
+          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7c175920fe1515</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a84e5fecd3d8a56</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f51834cb7830783</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Full Stack Engineer, Batch Operations</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06941a936b5627f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4e05d25284fdf864</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbd6eb878651cec7</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319f7679b0c236b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98788b7051be7608</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269f6b09b3801d42</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be632d37eec0b45</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd7ad62dd171a18</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85df90bb6dfbfae8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e11ec725a2ebb03</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eada5f5f6db8d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=258bed23fe0cbda2</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e819a7e5906d69f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b862bc47d421e21</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db5fbc30263e47f</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e3a8e2d05c0771</t>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Platforms Engineer II</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Oshkosh, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,3190 +5011,75 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer Mid or Senior</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Socure</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Carson City, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1821921db4210a68</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d82519a3cff7a03c</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48aa35823006036d</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2409f88dc2bb6479</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05589bd86f6613ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5bbf7634b17efe</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=842b00d75a1fdb78</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6426664fe876ccf0</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1e283728ccf2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da466b24aa8b8f93</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=171623610154829e</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Jericho, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bad93f8dd31cb04f</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6531397ce3761368</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b74c85c575d7d6ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c4599945fd6770f</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c2f5e00614cd1e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f61287d3dfc60c6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71c3abbc6d6ae00c</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca0a972a4b0fc1ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9fe046872a5db1</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63dc4567cdb8f559</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81a5e57062f4e1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0b7df132fd9dd3</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5681ee5fb7bccc</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Lansing, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efde12506dd5e02e</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d92d7fbbbc81d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ed8322b5b26962</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f7de5560f7c15c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fef70d9dc7c7945e</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1dddfb2596b7d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02a9496819a565</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d55e53d1a36497d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e29080468d4f19</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=000b04871f739cd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41ab2f0cbeb867c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d314e0fbc6c7255a</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff5a5de7290a2c8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5794a14a29c1f8c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7c1c8f63656a2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7482709c6153e607</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d47ad9f886f7d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f52ec397c45d4e1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a30e01f59bf80aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec7b21cec928d78</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48557644ca27af91</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38816cfaaf11a6ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Cloud Database Administrator- Project Delivery Specialist</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23bfa150bf370564</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Assistant Database Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Software Engineer II - AI Solutions</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>King of Prussia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>U.S. Marine Corps</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Quantico, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>OptiTrack</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>OptiTrack</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>OptiTrack</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Investment Compliance Engineer</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Apollo</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Socure</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Carson City, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Highlights for Children</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>isolved</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Nixa, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>PIMS Data Analyst</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Bechtel</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>DevOps Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Mister Car Wash</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Tucson, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=414fb4f6d3a8dcd9</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Software Engineer III (CJIS)</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>County of San Luis Obispo</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, SQL Server, MySQL, DynamoDB, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cda7602e4b5904c</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer, Batch Operations</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>RDS, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e05d25284fdf864</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Software Developer - Information Governance</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Epiq</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>PowerBI Developer</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Prologis</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Anteriad</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Apptronik</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Data/ Application Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Charlie's Produce</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>CERTIFID</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185c1836bede91b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cedfc80fbfee214</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Sevita</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Java Kafka Streams Developer</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>BI Developer Mid or Senior</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Progressive</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics &amp; BI Spclst 3 or Sr</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e958aba48d0575</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59c6b7befce247af</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Frame Foxes Creative</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frame Foxes Creative</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c464e383e34580</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4886c7943d95fde</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2cd6ff1af9152f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd026ed04aff3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1443de690608f973</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafe5f457265140c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0c9efe263252c2</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134da4ed5371e690</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cec5522637756cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bce59916a631c229</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9800315a487a07</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=944c909e8090f77c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f08c0f9ab8ce8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63bc0adc99f8a24b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f643c2f9e2f8e875</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff781ad106bf00e</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e7e3a50b44eadc</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95cfc0fb1f0052b</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=237407f225bdbdde</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee5fb899d70bb38</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a61b9f987d8319</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77dcd59570e17714</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=281137e24698eadf</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef1c49ca890a02d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a7925bf814317b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db200a070bd6f170</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e48f3b0c65cee2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84570080ccefe4b</t>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415547713e005c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec000a9308e1a29</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1ea9f10fd1fc07</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a80a106f8cc412</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a49b62e5c57fb30</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Ads Targeting Data Engineer, Ads Core</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98585cc9b7a9700</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db2953c1e3b688</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7c175920fe1515</t>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a84e5fecd3d8a56</t>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f51834cb7830783</t>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,2107 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06941a936b5627f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbd6eb878651cec7</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=319f7679b0c236b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98788b7051be7608</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=269f6b09b3801d42</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7be632d37eec0b45</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd7ad62dd171a18</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85df90bb6dfbfae8</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e11ec725a2ebb03</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7eada5f5f6db8d5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=258bed23fe0cbda2</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e819a7e5906d69f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b862bc47d421e21</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0db5fbc30263e47f</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Cloud Platforms Engineer II</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Amcor</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Oshkosh, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Power BI, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a5bd8b939af9f70</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Books-A-Million</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>AWS Cloud Architect - Remote - Contract</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Navat Technologies Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21d6094d4c650121</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Socure</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Carson City, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1821921db4210a68</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Assistant Database Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Software Engineer II - AI Solutions</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>King of Prussia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>OptiTrack</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>OptiTrack</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>OptiTrack</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Investment Compliance Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Apollo</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>U.S. Marine Corps</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Quantico, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>California State Personnel Board</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Socure</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Carson City, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Highlights for Children</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>isolved</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Nixa, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Azure Cosmos DB, NoSQL, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d13a0d2142e0261</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>PIMS Data Analyst</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Bechtel</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer, Batch Operations</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e05d25284fdf864</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Mashura</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>PowerBI Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Prologis</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Anteriad</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Apptronik</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data/ Application Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Charlie's Produce</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>CERTIFID</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Developer - Information Governance</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Epiq</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Sevita</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Java Kafka Streams Developer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>BI Developer Mid or Senior</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Progressive</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdbb236dac23c233</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frame Foxes Creative</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Frame Foxes Creative</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,29 +2446,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, MS Excel, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ads Targeting Data Engineer, Ads Core</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Airflow, Python</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2adeacdfffb183</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2945,41 +2945,6 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Java Kafka Streams Developer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,15 +2936,155 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>AWS ARCHITECT E-COMMERCE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Storage Asset Management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc27b8ad561d2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2dd02ca9d5cc68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc27b8ad561d2ae</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
+          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f16d1c6de9e445f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics &amp; BI Spclst 3 or Sr</t>
+          <t>Data Architect III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
+          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Frame Foxes Creative</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frame Foxes Creative</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
+          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
         </is>
       </c>
     </row>
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
+          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java API Gateway Developer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Investment Compliance Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Warranty Data Analyst / Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>PIMS Data Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Apptronik</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data/ Application Integration Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Charlie's Produce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28a43a00c1a7844</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Air Apps</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=da7d5c56b94e4648</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics &amp; BI Spclst 3 or Sr</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect III</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Glastonbury, CT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e958aba48d0575</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Glastonbury, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=861b456826f5b0c4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAI (Computer Aid, Inc.)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Suvoda</t>
+          <t>CAI (Computer Aid, Inc.)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
+          <t>https://www.indeed.com/viewjob?jk=69655961f8c3abc9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, ECS, RDS, Scala, Kafka, MySQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=a09c947868c141e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b69a2cd2e20538</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suvoda</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6fc79a37f3e06f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Senior Product Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=84317bbfd5f19a2b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=59c6b7befce247af</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frame Foxes Creative</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=708504cdbe336a34</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Java API Gateway Developer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java API Gateway Developer</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,112 +1431,112 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,137 +1581,137 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS, Scala, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a59c922032170a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=90c464e383e34580</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=d4886c7943d95fde</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2cd6ff1af9152f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd026ed04aff3f7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=1443de690608f973</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=fafe5f457265140c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0c9efe263252c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=134da4ed5371e690</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8cec5522637756cf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=bce59916a631c229</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9800315a487a07</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+          <t>https://www.indeed.com/viewjob?jk=944c909e8090f77c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PIMS Data Analyst</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f08c0f9ab8ce8d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=63bc0adc99f8a24b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f643c2f9e2f8e875</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff781ad106bf00e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e7e3a50b44eadc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d95cfc0fb1f0052b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=237407f225bdbdde</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=eee5fb899d70bb38</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a61b9f987d8319</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apptronik</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+          <t>https://www.indeed.com/viewjob?jk=77dcd59570e17714</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data/ Application Integration Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charlie's Produce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Oracle, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca44b855356ccf40</t>
+          <t>https://www.indeed.com/viewjob?jk=281137e24698eadf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef1c49ca890a02d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a7925bf814317b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Air Apps</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7d5c56b94e4648</t>
+          <t>https://www.indeed.com/viewjob?jk=db200a070bd6f170</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=85e48f3b0c65cee2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+          <t>https://www.indeed.com/viewjob?jk=d84570080ccefe4b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+          <t>https://www.indeed.com/viewjob?jk=415547713e005c9b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,40 +3051,2525 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=dec000a9308e1a29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e1ea9f10fd1fc07</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a80a106f8cc412</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a49b62e5c57fb30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e98585cc9b7a9700</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15db2953c1e3b688</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d7c175920fe1515</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a84e5fecd3d8a56</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f51834cb7830783</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06941a936b5627f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbd6eb878651cec7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=319f7679b0c236b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98788b7051be7608</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=269f6b09b3801d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7be632d37eec0b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fd7ad62dd171a18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85df90bb6dfbfae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e11ec725a2ebb03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eada5f5f6db8d5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=258bed23fe0cbda2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e819a7e5906d69f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b862bc47d421e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Forward Deployed Engineer/Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0db5fbc30263e47f</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Books-A-Million</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Cloud Engineer III</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AWS Cloud Architect - Remote - Contract</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Navat Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, API Gateway, IAM, RDS, Scala, PostgreSQL, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21d6094d4c650121</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - International eKYC, Identity Graph</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1821921db4210a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af1b1fc3dca61daa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AWS Integration Architect (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Signet Jewelers</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Coppell, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb0ac24378fc5967</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hightower Advisors</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f56b57a377fe3a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer II - AI Solutions</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Investment Compliance Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Apollo</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>U.S. Marine Corps</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Quantico, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Assistant Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sr Analyst, Data Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Socure</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>California State Personnel Board</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Highlights for Children</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PIMS Data Analyst</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Bechtel</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84332d95fe089578</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer, Batch Operations</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e05d25284fdf864</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Product Analytics (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Renew home</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, ECS, BigQuery, Dimensional Modeling, ETL, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94ce26cd728861e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Developer - Information Governance</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Analytics Solution Associate</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Mashura</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PowerBI Developer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Cloud &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Prologis</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Anteriad</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Apptronik</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, PostgreSQL, NoSQL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CERTIFID</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c509a2c5d165cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16029f18260b23a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Scala, DynamoDB, Amazon QuickSight, MLOps</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=585c6ab4414e23c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Event Streaming Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BDIPlus</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Java Kafka Streams Developer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Kafka, DynamoDB, ETL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc497768586e778b</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>DriveTime Automotive Group</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D147" t="n">
         <v>10.4</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics &amp; BI Spclst 3 or Sr</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>ML Engineering Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5fdb5e00e6bd271</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd13d9bc2495c26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,242 +2316,242 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3ce7aadbafa8d37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Automation</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,42 +2596,567 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Analytics Solution Associate</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mashura</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PowerBI Developer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Cloud &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Prologis</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Anteriad</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CERTIFID</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Developer - Information Governance</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Event Streaming Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BDIPlus</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>DriveTime Automotive Group</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D77" t="n">
         <v>10.4</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer – AWS Lakehouse (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>S-Techinfo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics &amp; BI Spclst 3 or Sr</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ML Engineering Consultant</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineering Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>NitinX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fdb5e00e6bd271</t>
+          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=d5fdb5e00e6bd271</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd13d9bc2495c26</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Applications Architect (C. Advanced)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Site Reliability Engineer (SRE) – II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,137 +1546,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2031,29 +2031,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,174 +2096,174 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3ce7aadbafa8d37</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Containers / EKS Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Automation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,77 +2621,77 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Cloud Storage, SQL Server, ETL, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d15d053831e0a70</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,120 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ML Engineering Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ML Engineering Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,52 +871,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>U.S. Marine Corps</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quantico, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Containers / EKS Specialist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Containers / EKS Specialist</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Senior Software Engineer, Automation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,69 +2726,69 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,120 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9d7f98d5bdda0c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fdb5e00e6bd271</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=d5fdb5e00e6bd271</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applications Architect (C. Advanced)</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) – II</t>
+          <t>Applications Architect (C. Advanced)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
+          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Site Reliability Engineer (SRE) – II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Barceloneta, PR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Sr IT Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SENIOR ENTERPRISE DATA ARCHITECT</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Marine Corps</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Quantico, VA, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3977bc6913228407</t>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Spark, Scala, Snowflake, ETL, Maven</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Containers / EKS Specialist</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Containers / EKS Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
+          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Automation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,52 +2726,52 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Software Developer - Information Governance</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,122 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr. Development Support Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Radiology Partners</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,104 +486,104 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,147 +591,147 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer – AWS Lakehouse (Remote)</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S-Techinfo</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, SQS, Databricks, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18335be1419a92a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics &amp; BI Spclst 3 or Sr</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>ML Engineering Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9d7f98d5bdda0c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ML Engineering Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9d7f98d5bdda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5fdb5e00e6bd271</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Applications Architect (C. Advanced)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=21f79af4f138986f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Applications Architect (C. Advanced)</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Software Engineer, DFIR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,104 +1326,104 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa30285abbf1788b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barceloneta, PR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1dcac7054b0073</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Omni Hotels</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, Star Schema, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala, DynamoDB</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Sr IT Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr IT Analyst</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2031,29 +2031,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Engineer - Data &amp; ML Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,139 +2131,139 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494f58d930e8174f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Cloud Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9177734e7ea91a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Containers / EKS Specialist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Containers / EKS Specialist</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Senior Software Engineer, Automation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, NoSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Git, SQL</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud &amp; AI Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,120 +3356,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Sevita</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,122 +468,122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>AWS ARCHITECT E-COMMERCE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Storage Asset Management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2dd02ca9d5cc68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Data Architect III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e958aba48d0575</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Engineering Consultant</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9d7f98d5bdda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Engineering Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KUBRA</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
+          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9d7f98d5bdda0c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=01d1e673d73274cb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>KUBRA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2a9614a79aed2a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Applications Architect (C. Advanced)</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f79af4f138986f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Applications Architect (C. Advanced)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Tech Army</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) – II</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
+          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, DFIR</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tokio Marine HCC</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,64 +1326,64 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa30285abbf1788b</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Site Reliability Engineer (SRE) – II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=21f79af4f138986f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, DFIR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=aa30285abbf1788b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb3950a15b093b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr IT Analyst</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Sr IT Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=408b75423e54b3b2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; ML Platform</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Databricks, Spark, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,174 +2131,174 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Assistant Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Cloud Architect</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9177734e7ea91a</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Containers / EKS Specialist</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>Sr Cloud Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9177734e7ea91a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Containers / EKS Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java Kafka Streams Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,77 +2761,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Senior Software Engineer, Automation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>The Joint Commission</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CERTIFID</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr. Data Engineer (Hybrid or Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mashura</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Event Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,192 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Event Streaming Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BDIPlus</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sr. Development Support Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Radiology Partners</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Integration Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sevita</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-24.xlsx
+++ b/results/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS ARCHITECT E-COMMERCE</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage Asset Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Azure, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,207 +496,207 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2dd02ca9d5cc68</t>
+          <t>https://www.indeed.com/viewjob?jk=5b44724ef07bf0a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Java Application Support Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=a6887fcec2e6909c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Java Application Support Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1240d3e0b18e47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
+          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=97183c81227864b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>10X Genomics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Medallion Architecture, GCP, Cloud Storage, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,164 +706,164 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0eff69119214bd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e958aba48d0575</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Databricks Senior Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=70901457c8624077</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e197aeed7a4daa68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clarivate</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ML Engineering Consultant</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,52 +871,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Clarivate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Scala, SQL Server, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9d7f98d5bdda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=93aadd8b0c9c7d51</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - AI</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
+          <t>https://www.indeed.com/viewjob?jk=0703e81fbc55d324</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
+          <t>https://www.indeed.com/viewjob?jk=efe7e953ddc656aa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcd15cbd7eca85e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tech Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
+          <t>https://www.indeed.com/viewjob?jk=decac87a41515867</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Engineer III</t>
+          <t>Sr Data Engineer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
+          <t>https://www.indeed.com/viewjob?jk=7dac16853e3a0a45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Applications Architect (C. Advanced)</t>
+          <t>Tech Platform Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, SQL Server, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859c1fde04a1f7bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c96f6146028ac0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Platform Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, S3, IAM, Spark, PySpark, Scala, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
+          <t>https://www.indeed.com/viewjob?jk=e8d740e303897a44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Remote</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Healthcare Data Engineer - Eligibility &amp; Integrations (Microsoft Fabric)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=77a67e04b39a994b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) – II</t>
+          <t>Senior Data Platform Engineer, Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,104 +1396,104 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, EMR, RDS, Hive, HBase, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
+          <t>https://www.indeed.com/viewjob?jk=977bf1988c99ef2b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f79af4f138986f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, DFIR</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tokio Marine HCC</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa30285abbf1788b</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf71cb97b6bf7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6859308e43774778</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Event Hubs, Scala, Kafka, Snowflake, ETL, Talend, Pentaho</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c755a205934bcc5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, ETL, ELT, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0d606381807625</t>
+          <t>https://www.indeed.com/viewjob?jk=b6837d4a932a91bd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a100ab935210c730</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=a20313f7d2a7a9dc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd91e562ca9970a9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,94 +1756,94 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Senior - Shared Services</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Ware Malcomb</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8af61c6f890c0f1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
+          <t>Site Reliability Engineer, Senior - Shared Services</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
+          <t>https://www.indeed.com/viewjob?jk=f039036773c1f28e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Sr Site Reliability Engineer (Advanced Threat Protection)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
+          <t>https://www.indeed.com/viewjob?jk=c75f571426bd8624</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr IT Analyst</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4d209e381e858e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408b75423e54b3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4193f3fe77904a35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4214ccb3eede4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3db9aa6186a43</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2cfc17e75f7401</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Sr IT Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=0afe088d065fd78d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d3fcca45b625b2</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2171,72 +2171,72 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7ff9f54a3bf3df2</t>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8dbd90f5c708f902</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Assistant Database Reliability Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, ETL, Splunk, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e260e9d5d3946a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java QA Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Red Cat Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
+          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Java QA Automation Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=8462ced5ab30fab8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Data Scientist - Big Data R&amp;D, Identity Graph &amp; KYC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, RDS, Databricks, Spark, PySpark, Scala, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=71af9298e33a2a39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Test Engineer (JUnit, TestNG)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Red Cat Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1070b79a3524d7</t>
+          <t>https://www.indeed.com/viewjob?jk=121388def99607e8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Java Test Engineer (JUnit, TestNG)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Snowflake, SQL Server, ETL, Microsoft SSIS, Power BI</t>
+          <t>AWS, Scala, Snowflake, ETL, Talend, Power BI, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=799c882a39511da7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Cloud Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>Highlights for Children</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9177734e7ea91a</t>
+          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Engineer-5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
+          <t>https://www.indeed.com/viewjob?jk=62e5d4bfa811f4f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Containers / EKS Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccdb683ece378a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c943add79570b0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,24 +2691,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
+          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Kafka Streams Developer</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Cloud Storage, Hadoop, Spark, Scala, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b56d1e86b842b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d00cf36f39bc489</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Highlights for Children</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da776d40fc886409</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b7ab7604cd46281</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Analytics Solution Associate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20f01e742321cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Berkshire Hathaway Direct Insurance Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Terraform, Docker, Kubernetes, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Joint Commission</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813d5ada1f8fd5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>CERTIFID</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Event Streaming Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, BigQuery, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Solution Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, Tableau, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682f448ab80fc1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Direct Insurance Company</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef096b1b6b717ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid or Remote)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mashura</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f082901e3e3db300</t>
+          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,367 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e69028d79bb8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>CERTIFID</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Kafka, Snowflake, clustering keys, Dimensional Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f20b957dca19c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI Testing Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Select Minds LLC</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Java Trainer / Mentor / Educator</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Java Trainer / Mentor / Educator</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Kafka, NoSQL, CI/CD, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Event Streaming Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Kafka, Kafka Connect, Terraform</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr. Development Support Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Radiology Partners</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Sevita</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Kafka, Kafka Connect, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e4643d6e89461e</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b253315d0e7f0790</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c181449ffb89883</t>
         </is>
       </c>
     </row>
